--- a/public/estochabitatge.xlsx
+++ b/public/estochabitatge.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAEF8C21-595F-4241-9D80-2AAADE293EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F612D530-066C-4D4E-BA8C-11043B2DE3F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -677,10 +677,10 @@
       </c>
       <c r="B2" s="3">
         <f>(C2*100/D2)-100</f>
-        <v>29.865125240847789</v>
+        <v>27.222680979906414</v>
       </c>
       <c r="C2" s="11">
-        <v>4718</v>
+        <v>4622</v>
       </c>
       <c r="D2" s="11">
         <v>3633</v>
@@ -699,7 +699,7 @@
       </c>
       <c r="I2" s="3">
         <f>(C2*100/H2)-100</f>
-        <v>-63.771788374414498</v>
+        <v>-64.508945711433626</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -708,10 +708,10 @@
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B7" si="0">(C3*100/D3)-100</f>
-        <v>-7.9189926002856055</v>
+        <v>-9.042521803783643</v>
       </c>
       <c r="C3" s="11">
-        <v>78023</v>
+        <v>77071</v>
       </c>
       <c r="D3" s="11">
         <v>84733</v>
@@ -730,7 +730,7 @@
       </c>
       <c r="I3" s="3">
         <f t="shared" ref="I3:I7" si="1">(C3*100/H3)-100</f>
-        <v>-46.257749001239837</v>
+        <v>-46.913486706157876</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -739,10 +739,10 @@
       </c>
       <c r="B4" s="3">
         <f t="shared" si="0"/>
-        <v>11.586623453152626</v>
+        <v>9.295816146140254</v>
       </c>
       <c r="C4" s="11">
-        <v>15149</v>
+        <v>14838</v>
       </c>
       <c r="D4" s="11">
         <v>13576</v>
@@ -761,7 +761,7 @@
       </c>
       <c r="I4" s="3">
         <f t="shared" si="1"/>
-        <v>-34.57568559706327</v>
+        <v>-35.918808032822284</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -770,10 +770,10 @@
       </c>
       <c r="B5" s="3">
         <f t="shared" si="0"/>
-        <v>-6.2858186633787767</v>
+        <v>-7.5735780989565455</v>
       </c>
       <c r="C5" s="11">
-        <v>82088</v>
+        <v>80960</v>
       </c>
       <c r="D5" s="11">
         <v>87594</v>
@@ -792,7 +792,7 @@
       </c>
       <c r="I5" s="3">
         <f t="shared" si="1"/>
-        <v>-30.188968074430633</v>
+        <v>-31.148265950028062</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -801,10 +801,10 @@
       </c>
       <c r="B6" s="3">
         <f t="shared" si="0"/>
-        <v>-7.3350416399743779</v>
+        <v>-8.3920563741191501</v>
       </c>
       <c r="C6" s="11">
-        <v>2893</v>
+        <v>2860</v>
       </c>
       <c r="D6" s="11">
         <v>3122</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="I6" s="3">
         <f t="shared" si="1"/>
-        <v>-51.410816257977828</v>
+        <v>-51.965065502183407</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -832,10 +832,10 @@
       </c>
       <c r="B7" s="3">
         <f t="shared" si="0"/>
-        <v>-6.5409570154095746</v>
+        <v>-7.4614760746147653</v>
       </c>
       <c r="C7" s="11">
-        <v>23047</v>
+        <v>22820</v>
       </c>
       <c r="D7" s="11">
         <v>24660</v>
@@ -854,7 +854,7 @@
       </c>
       <c r="I7" s="3">
         <f t="shared" si="1"/>
-        <v>-35.648070586921321</v>
+        <v>-36.281900932596194</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -896,10 +896,10 @@
       </c>
       <c r="B10" s="3">
         <f>(C10*100/D10)-100</f>
-        <v>12.905718701700152</v>
+        <v>9.119010819165382</v>
       </c>
       <c r="C10" s="11">
-        <v>2922</v>
+        <v>2824</v>
       </c>
       <c r="D10" s="9">
         <v>2588</v>
@@ -918,7 +918,7 @@
       </c>
       <c r="I10" s="3">
         <f>(C10*100/H10)-100</f>
-        <v>-52.035456336178598</v>
+        <v>-53.644123440577808</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -927,10 +927,10 @@
       </c>
       <c r="B11" s="3">
         <f t="shared" ref="B11:B15" si="2">(C11*100/D11)-100</f>
-        <v>19.515389652914209</v>
+        <v>16.9145850874731</v>
       </c>
       <c r="C11" s="11">
-        <v>12775</v>
+        <v>12497</v>
       </c>
       <c r="D11" s="9">
         <v>10689</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="I11" s="3">
         <f t="shared" ref="I11:I15" si="3">(C11*100/H11)-100</f>
-        <v>-19.517419517419512</v>
+        <v>-21.26882126882127</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -958,10 +958,10 @@
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>0.14059048001607266</v>
+        <v>-7.4713797951395833</v>
       </c>
       <c r="C12" s="11">
-        <v>4986</v>
+        <v>4607</v>
       </c>
       <c r="D12" s="9">
         <v>4979</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="I12" s="3">
         <f t="shared" si="3"/>
-        <v>-72.963886780175685</v>
+        <v>-75.018978418826592</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -989,10 +989,10 @@
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>7.2307497145756656</v>
+        <v>0.93872891031332983</v>
       </c>
       <c r="C13" s="11">
-        <v>8453</v>
+        <v>7957</v>
       </c>
       <c r="D13" s="9">
         <v>7883</v>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="I13" s="3">
         <f t="shared" si="3"/>
-        <v>-64.352886602285665</v>
+        <v>-66.444566271665337</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -1020,10 +1020,10 @@
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>30.900621118012424</v>
+        <v>31.83229813664596</v>
       </c>
       <c r="C14" s="11">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="D14" s="9">
         <v>644</v>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="I14" s="3">
         <f t="shared" si="3"/>
-        <v>-67.861227601982463</v>
+        <v>-67.632481890964542</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -1051,10 +1051,10 @@
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>29.142692750287694</v>
+        <v>28.365937859608749</v>
       </c>
       <c r="C15" s="11">
-        <v>4489</v>
+        <v>4462</v>
       </c>
       <c r="D15" s="9">
         <v>3476</v>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="I15" s="3">
         <f t="shared" si="3"/>
-        <v>-43.725711420333461</v>
+        <v>-44.06418453052526</v>
       </c>
     </row>
   </sheetData>

--- a/public/estochabitatge.xlsx
+++ b/public/estochabitatge.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F612D530-066C-4D4E-BA8C-11043B2DE3F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3845343-A804-4174-ABB5-35F362DAE6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -623,26 +623,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE0A71B-F9FA-4E45-8679-5B51BE4A2368}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.6328125" customWidth="1"/>
-    <col min="2" max="3" width="12.7265625" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="16.08984375" customWidth="1"/>
-    <col min="7" max="7" width="14.08984375" customWidth="1"/>
-    <col min="8" max="8" width="14.54296875" customWidth="1"/>
-    <col min="9" max="9" width="22.6328125" customWidth="1"/>
-    <col min="10" max="10" width="10.7265625" customWidth="1"/>
-    <col min="11" max="11" width="14.453125" customWidth="1"/>
-    <col min="12" max="12" width="12.453125" customWidth="1"/>
-    <col min="13" max="13" width="12.36328125" customWidth="1"/>
-    <col min="14" max="14" width="11.6328125" customWidth="1"/>
-    <col min="15" max="15" width="12.08984375" customWidth="1"/>
+    <col min="2" max="4" width="12.7265625" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="16.08984375" customWidth="1"/>
+    <col min="8" max="8" width="14.08984375" customWidth="1"/>
+    <col min="9" max="9" width="14.54296875" customWidth="1"/>
+    <col min="10" max="10" width="22.6328125" customWidth="1"/>
+    <col min="11" max="11" width="10.7265625" customWidth="1"/>
+    <col min="12" max="12" width="14.453125" customWidth="1"/>
+    <col min="13" max="13" width="12.453125" customWidth="1"/>
+    <col min="14" max="14" width="12.36328125" customWidth="1"/>
+    <col min="15" max="15" width="11.6328125" customWidth="1"/>
+    <col min="16" max="16" width="12.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -650,90 +650,96 @@
         <v>1</v>
       </c>
       <c r="C1" s="7">
+        <f ca="1">TODAY()</f>
+        <v>46063</v>
+      </c>
+      <c r="D1" s="7">
         <v>46023</v>
       </c>
-      <c r="D1" s="7">
+      <c r="E1" s="7">
         <v>45658</v>
       </c>
-      <c r="E1" s="7">
+      <c r="F1" s="7">
         <v>45292</v>
       </c>
-      <c r="F1" s="7">
+      <c r="G1" s="7">
         <v>44927</v>
       </c>
-      <c r="G1" s="7">
+      <c r="H1" s="7">
         <v>44562</v>
       </c>
-      <c r="H1" s="7">
+      <c r="I1" s="7">
         <v>44197</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <f>(C2*100/D2)-100</f>
+        <f>(D2*100/E2)-100</f>
         <v>27.222680979906414</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="3"/>
+      <c r="D2" s="11">
         <v>4622</v>
       </c>
-      <c r="D2" s="11">
+      <c r="E2" s="11">
         <v>3633</v>
       </c>
-      <c r="E2" s="12">
+      <c r="F2" s="12">
         <v>5351</v>
       </c>
-      <c r="F2" s="11">
+      <c r="G2" s="11">
         <v>7856</v>
       </c>
-      <c r="G2" s="11">
+      <c r="H2" s="11">
         <v>10352</v>
       </c>
-      <c r="H2" s="12">
+      <c r="I2" s="12">
         <v>13023</v>
       </c>
-      <c r="I2" s="3">
-        <f>(C2*100/H2)-100</f>
+      <c r="J2" s="3">
+        <f>(D2*100/I2)-100</f>
         <v>-64.508945711433626</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="3">
-        <f t="shared" ref="B3:B7" si="0">(C3*100/D3)-100</f>
+        <f t="shared" ref="B3:B7" si="0">(D3*100/E3)-100</f>
         <v>-9.042521803783643</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="3"/>
+      <c r="D3" s="11">
         <v>77071</v>
       </c>
-      <c r="D3" s="11">
+      <c r="E3" s="11">
         <v>84733</v>
       </c>
-      <c r="E3" s="12">
+      <c r="F3" s="12">
         <v>105781</v>
       </c>
-      <c r="F3" s="11">
+      <c r="G3" s="11">
         <v>120344</v>
       </c>
-      <c r="G3" s="11">
+      <c r="H3" s="11">
         <v>140667</v>
       </c>
-      <c r="H3" s="12">
+      <c r="I3" s="12">
         <v>145180</v>
       </c>
-      <c r="I3" s="3">
-        <f t="shared" ref="I3:I7" si="1">(C3*100/H3)-100</f>
+      <c r="J3" s="3">
+        <f t="shared" ref="J3:J7" si="1">(D3*100/I3)-100</f>
         <v>-46.913486706157876</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -741,30 +747,31 @@
         <f t="shared" si="0"/>
         <v>9.295816146140254</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="3"/>
+      <c r="D4" s="11">
         <v>14838</v>
       </c>
-      <c r="D4" s="11">
+      <c r="E4" s="11">
         <v>13576</v>
       </c>
-      <c r="E4" s="12">
+      <c r="F4" s="12">
         <v>18134</v>
       </c>
-      <c r="F4" s="11">
+      <c r="G4" s="11">
         <v>22107</v>
       </c>
-      <c r="G4" s="11">
+      <c r="H4" s="11">
         <v>24750</v>
       </c>
-      <c r="H4" s="12">
+      <c r="I4" s="12">
         <v>23155</v>
       </c>
-      <c r="I4" s="3">
+      <c r="J4" s="3">
         <f t="shared" si="1"/>
         <v>-35.918808032822284</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
         <v>0</v>
       </c>
@@ -772,30 +779,31 @@
         <f t="shared" si="0"/>
         <v>-7.5735780989565455</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="3"/>
+      <c r="D5" s="11">
         <v>80960</v>
       </c>
-      <c r="D5" s="11">
+      <c r="E5" s="11">
         <v>87594</v>
       </c>
-      <c r="E5" s="12">
+      <c r="F5" s="12">
         <v>108194</v>
       </c>
-      <c r="F5" s="11">
+      <c r="G5" s="11">
         <v>113475</v>
       </c>
-      <c r="G5" s="11">
+      <c r="H5" s="11">
         <v>113522</v>
       </c>
-      <c r="H5" s="12">
+      <c r="I5" s="12">
         <v>117586</v>
       </c>
-      <c r="I5" s="3">
+      <c r="J5" s="3">
         <f t="shared" si="1"/>
         <v>-31.148265950028062</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
@@ -803,30 +811,31 @@
         <f t="shared" si="0"/>
         <v>-8.3920563741191501</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="3"/>
+      <c r="D6" s="11">
         <v>2860</v>
       </c>
-      <c r="D6" s="11">
+      <c r="E6" s="11">
         <v>3122</v>
       </c>
-      <c r="E6" s="12">
+      <c r="F6" s="12">
         <v>4116</v>
       </c>
-      <c r="F6" s="11">
+      <c r="G6" s="11">
         <v>4802</v>
       </c>
-      <c r="G6" s="11">
+      <c r="H6" s="11">
         <v>5513</v>
       </c>
-      <c r="H6" s="12">
+      <c r="I6" s="12">
         <v>5954</v>
       </c>
-      <c r="I6" s="3">
+      <c r="J6" s="3">
         <f t="shared" si="1"/>
         <v>-51.965065502183407</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
@@ -834,34 +843,35 @@
         <f t="shared" si="0"/>
         <v>-7.4614760746147653</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="3"/>
+      <c r="D7" s="11">
         <v>22820</v>
       </c>
-      <c r="D7" s="11">
+      <c r="E7" s="11">
         <v>24660</v>
       </c>
-      <c r="E7" s="12">
+      <c r="F7" s="12">
         <v>28929</v>
       </c>
-      <c r="F7" s="11">
+      <c r="G7" s="11">
         <v>29223</v>
       </c>
-      <c r="G7" s="11">
+      <c r="H7" s="11">
         <v>31497</v>
       </c>
-      <c r="H7" s="12">
+      <c r="I7" s="12">
         <v>35814</v>
       </c>
-      <c r="I7" s="3">
+      <c r="J7" s="3">
         <f t="shared" si="1"/>
         <v>-36.281900932596194</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="F8" s="8"/>
-      <c r="H8" s="6"/>
-    </row>
-    <row r="9" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G8" s="8"/>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -869,90 +879,96 @@
         <v>1</v>
       </c>
       <c r="C9" s="7">
+        <f ca="1">TODAY()</f>
+        <v>46063</v>
+      </c>
+      <c r="D9" s="7">
         <v>46023</v>
       </c>
-      <c r="D9" s="7">
+      <c r="E9" s="7">
         <v>45658</v>
       </c>
-      <c r="E9" s="7">
+      <c r="F9" s="7">
         <v>45292</v>
       </c>
-      <c r="F9" s="7">
+      <c r="G9" s="7">
         <v>44927</v>
       </c>
-      <c r="G9" s="7">
+      <c r="H9" s="7">
         <v>44562</v>
       </c>
-      <c r="H9" s="7">
+      <c r="I9" s="7">
         <v>44197</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="J9" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="3">
-        <f>(C10*100/D10)-100</f>
+        <f>(D10*100/E10)-100</f>
         <v>9.119010819165382</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="3"/>
+      <c r="D10" s="11">
         <v>2824</v>
       </c>
-      <c r="D10" s="9">
+      <c r="E10" s="9">
         <v>2588</v>
       </c>
-      <c r="E10" s="9">
+      <c r="F10" s="9">
         <v>2100</v>
       </c>
-      <c r="F10" s="9">
+      <c r="G10" s="9">
         <v>1593</v>
       </c>
-      <c r="G10" s="9">
+      <c r="H10" s="9">
         <v>2709</v>
       </c>
-      <c r="H10" s="10">
+      <c r="I10" s="10">
         <v>6092</v>
       </c>
-      <c r="I10" s="3">
-        <f>(C10*100/H10)-100</f>
+      <c r="J10" s="3">
+        <f>(D10*100/I10)-100</f>
         <v>-53.644123440577808</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="3">
-        <f t="shared" ref="B11:B15" si="2">(C11*100/D11)-100</f>
+        <f t="shared" ref="B11:B15" si="2">(D11*100/E11)-100</f>
         <v>16.9145850874731</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="3"/>
+      <c r="D11" s="11">
         <v>12497</v>
       </c>
-      <c r="D11" s="9">
+      <c r="E11" s="9">
         <v>10689</v>
       </c>
-      <c r="E11" s="9">
+      <c r="F11" s="9">
         <v>9044</v>
       </c>
-      <c r="F11" s="9">
+      <c r="G11" s="9">
         <v>7708</v>
       </c>
-      <c r="G11" s="9">
+      <c r="H11" s="9">
         <v>9737</v>
       </c>
-      <c r="H11" s="10">
+      <c r="I11" s="10">
         <v>15873</v>
       </c>
-      <c r="I11" s="3">
-        <f t="shared" ref="I11:I15" si="3">(C11*100/H11)-100</f>
+      <c r="J11" s="3">
+        <f t="shared" ref="J11:J15" si="3">(D11*100/I11)-100</f>
         <v>-21.26882126882127</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="4" t="s">
         <v>2</v>
       </c>
@@ -960,30 +976,31 @@
         <f t="shared" si="2"/>
         <v>-7.4713797951395833</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="3"/>
+      <c r="D12" s="11">
         <v>4607</v>
       </c>
-      <c r="D12" s="9">
+      <c r="E12" s="9">
         <v>4979</v>
       </c>
-      <c r="E12" s="9">
+      <c r="F12" s="9">
         <v>5833</v>
       </c>
-      <c r="F12" s="9">
+      <c r="G12" s="9">
         <v>5809</v>
       </c>
-      <c r="G12" s="9">
+      <c r="H12" s="9">
         <v>6960</v>
       </c>
-      <c r="H12" s="10">
+      <c r="I12" s="10">
         <v>18442</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <f t="shared" si="3"/>
         <v>-75.018978418826592</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
         <v>0</v>
       </c>
@@ -991,30 +1008,31 @@
         <f t="shared" si="2"/>
         <v>0.93872891031332983</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="3"/>
+      <c r="D13" s="11">
         <v>7957</v>
       </c>
-      <c r="D13" s="9">
+      <c r="E13" s="9">
         <v>7883</v>
       </c>
-      <c r="E13" s="9">
+      <c r="F13" s="9">
         <v>9571</v>
       </c>
-      <c r="F13" s="9">
+      <c r="G13" s="9">
         <v>10067</v>
       </c>
-      <c r="G13" s="9">
+      <c r="H13" s="9">
         <v>10452</v>
       </c>
-      <c r="H13" s="10">
+      <c r="I13" s="10">
         <v>23713</v>
       </c>
-      <c r="I13" s="3">
+      <c r="J13" s="3">
         <f t="shared" si="3"/>
         <v>-66.444566271665337</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="4" t="s">
         <v>4</v>
       </c>
@@ -1022,30 +1040,31 @@
         <f t="shared" si="2"/>
         <v>31.83229813664596</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="3"/>
+      <c r="D14" s="11">
         <v>849</v>
       </c>
-      <c r="D14" s="9">
+      <c r="E14" s="9">
         <v>644</v>
       </c>
-      <c r="E14" s="9">
+      <c r="F14" s="9">
         <v>741</v>
       </c>
-      <c r="F14" s="9">
+      <c r="G14" s="9">
         <v>942</v>
       </c>
-      <c r="G14" s="9">
+      <c r="H14" s="9">
         <v>1414</v>
       </c>
-      <c r="H14" s="10">
+      <c r="I14" s="10">
         <v>2623</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <f t="shared" si="3"/>
         <v>-67.632481890964542</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="5" t="s">
         <v>5</v>
       </c>
@@ -1053,31 +1072,32 @@
         <f t="shared" si="2"/>
         <v>28.365937859608749</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="3"/>
+      <c r="D15" s="11">
         <v>4462</v>
       </c>
-      <c r="D15" s="9">
+      <c r="E15" s="9">
         <v>3476</v>
       </c>
-      <c r="E15" s="9">
+      <c r="F15" s="9">
         <v>3332</v>
       </c>
-      <c r="F15" s="9">
+      <c r="G15" s="9">
         <v>3606</v>
       </c>
-      <c r="G15" s="9">
+      <c r="H15" s="9">
         <v>4549</v>
       </c>
-      <c r="H15" s="10">
+      <c r="I15" s="10">
         <v>7977</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <f t="shared" si="3"/>
         <v>-44.06418453052526</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B7">
+  <conditionalFormatting sqref="B2:C7">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
@@ -1091,7 +1111,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B10:B15">
+  <conditionalFormatting sqref="B10:C15">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
@@ -1105,7 +1125,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="J2:J7">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -1119,7 +1139,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I10:I15">
+  <conditionalFormatting sqref="J10:J15">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -1162,7 +1182,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>B2:B7</xm:sqref>
+          <xm:sqref>B2:C7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{5DFD4702-AFA2-4D91-98CB-0AD8A93A7697}">
@@ -1175,7 +1195,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>B10:B15</xm:sqref>
+          <xm:sqref>B10:C15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{96C1573B-A030-48E0-B2A2-67E751F2AFDF}">
@@ -1188,7 +1208,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I7</xm:sqref>
+          <xm:sqref>J2:J7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{29352116-8E53-43B4-8488-612C04A5EB1A}">
@@ -1201,7 +1221,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I10:I15</xm:sqref>
+          <xm:sqref>J10:J15</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/public/estochabitatge.xlsx
+++ b/public/estochabitatge.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3845343-A804-4174-ABB5-35F362DAE6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C0B306-D4AC-4AFF-932E-2B1CD9D1EC27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -183,7 +183,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -226,6 +226,7 @@
     <xf numFmtId="17" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Enllaç" xfId="1" builtinId="8"/>
@@ -623,11 +624,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE0A71B-F9FA-4E45-8679-5B51BE4A2368}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.6328125" customWidth="1"/>
-    <col min="2" max="4" width="12.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" customWidth="1"/>
+    <col min="4" max="4" width="12.7265625" customWidth="1"/>
     <col min="5" max="5" width="15.453125" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="16.08984375" customWidth="1"/>
@@ -651,7 +654,7 @@
       </c>
       <c r="C1" s="7">
         <f ca="1">TODAY()</f>
-        <v>46063</v>
+        <v>46145</v>
       </c>
       <c r="D1" s="7">
         <v>46023</v>
@@ -680,10 +683,12 @@
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <f>(D2*100/E2)-100</f>
-        <v>27.222680979906414</v>
-      </c>
-      <c r="C2" s="3"/>
+        <f>(C2*100/D2)-100</f>
+        <v>11.661618347035912</v>
+      </c>
+      <c r="C2" s="11">
+        <v>5161</v>
+      </c>
       <c r="D2" s="11">
         <v>4622</v>
       </c>
@@ -703,8 +708,8 @@
         <v>13023</v>
       </c>
       <c r="J2" s="3">
-        <f>(D2*100/I2)-100</f>
-        <v>-64.508945711433626</v>
+        <f>(C2*100/I2)-100</f>
+        <v>-60.370114412961684</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -712,10 +717,12 @@
         <v>6</v>
       </c>
       <c r="B3" s="3">
-        <f t="shared" ref="B3:B7" si="0">(D3*100/E3)-100</f>
-        <v>-9.042521803783643</v>
-      </c>
-      <c r="C3" s="3"/>
+        <f t="shared" ref="B3:B7" si="0">(C3*100/D3)-100</f>
+        <v>0.72271022823110798</v>
+      </c>
+      <c r="C3" s="11">
+        <v>77628</v>
+      </c>
       <c r="D3" s="11">
         <v>77071</v>
       </c>
@@ -735,8 +742,8 @@
         <v>145180</v>
       </c>
       <c r="J3" s="3">
-        <f t="shared" ref="J3:J7" si="1">(D3*100/I3)-100</f>
-        <v>-46.913486706157876</v>
+        <f t="shared" ref="J3:J7" si="1">(C3*100/I3)-100</f>
+        <v>-46.529825044772004</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -745,9 +752,11 @@
       </c>
       <c r="B4" s="3">
         <f t="shared" si="0"/>
-        <v>9.295816146140254</v>
-      </c>
-      <c r="C4" s="3"/>
+        <v>1.5231163229545785</v>
+      </c>
+      <c r="C4" s="11">
+        <v>15064</v>
+      </c>
       <c r="D4" s="11">
         <v>14838</v>
       </c>
@@ -768,7 +777,7 @@
       </c>
       <c r="J4" s="3">
         <f t="shared" si="1"/>
-        <v>-35.918808032822284</v>
+        <v>-34.942776938026341</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -777,9 +786,11 @@
       </c>
       <c r="B5" s="3">
         <f t="shared" si="0"/>
-        <v>-7.5735780989565455</v>
-      </c>
-      <c r="C5" s="3"/>
+        <v>-2.6902173913043441</v>
+      </c>
+      <c r="C5" s="11">
+        <v>78782</v>
+      </c>
       <c r="D5" s="11">
         <v>80960</v>
       </c>
@@ -800,7 +811,7 @@
       </c>
       <c r="J5" s="3">
         <f t="shared" si="1"/>
-        <v>-31.148265950028062</v>
+        <v>-33.000527273655024</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -809,9 +820,11 @@
       </c>
       <c r="B6" s="3">
         <f t="shared" si="0"/>
-        <v>-8.3920563741191501</v>
-      </c>
-      <c r="C6" s="3"/>
+        <v>11.503496503496507</v>
+      </c>
+      <c r="C6" s="11">
+        <v>3189</v>
+      </c>
       <c r="D6" s="11">
         <v>2860</v>
       </c>
@@ -832,7 +845,7 @@
       </c>
       <c r="J6" s="3">
         <f t="shared" si="1"/>
-        <v>-51.965065502183407</v>
+        <v>-46.439368491770239</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -840,10 +853,12 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <f t="shared" si="0"/>
-        <v>-7.4614760746147653</v>
-      </c>
-      <c r="C7" s="3"/>
+        <f>(C7*100/D7)-100</f>
+        <v>0.82822085889570474</v>
+      </c>
+      <c r="C7" s="11">
+        <v>23009</v>
+      </c>
       <c r="D7" s="11">
         <v>22820</v>
       </c>
@@ -864,12 +879,13 @@
       </c>
       <c r="J7" s="3">
         <f t="shared" si="1"/>
-        <v>-36.281900932596194</v>
+        <v>-35.754174345228122</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="G8" s="8"/>
       <c r="I8" s="6"/>
+      <c r="J8" s="14"/>
     </row>
     <row r="9" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
@@ -880,7 +896,7 @@
       </c>
       <c r="C9" s="7">
         <f ca="1">TODAY()</f>
-        <v>46063</v>
+        <v>46145</v>
       </c>
       <c r="D9" s="7">
         <v>46023</v>
@@ -909,10 +925,12 @@
         <v>3</v>
       </c>
       <c r="B10" s="3">
-        <f>(D10*100/E10)-100</f>
-        <v>9.119010819165382</v>
-      </c>
-      <c r="C10" s="3"/>
+        <f>(C10*100/D10)-100</f>
+        <v>-1.0977337110481642</v>
+      </c>
+      <c r="C10" s="11">
+        <v>2793</v>
+      </c>
       <c r="D10" s="11">
         <v>2824</v>
       </c>
@@ -932,8 +950,8 @@
         <v>6092</v>
       </c>
       <c r="J10" s="3">
-        <f>(D10*100/I10)-100</f>
-        <v>-53.644123440577808</v>
+        <f>(C10*100/I10)-100</f>
+        <v>-54.152987524622453</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -941,10 +959,12 @@
         <v>6</v>
       </c>
       <c r="B11" s="3">
-        <f t="shared" ref="B11:B15" si="2">(D11*100/E11)-100</f>
-        <v>16.9145850874731</v>
-      </c>
-      <c r="C11" s="3"/>
+        <f t="shared" ref="B11:B15" si="2">(C11*100/D11)-100</f>
+        <v>-5.8013923341601981</v>
+      </c>
+      <c r="C11" s="11">
+        <v>11772</v>
+      </c>
       <c r="D11" s="11">
         <v>12497</v>
       </c>
@@ -964,8 +984,8 @@
         <v>15873</v>
       </c>
       <c r="J11" s="3">
-        <f t="shared" ref="J11:J15" si="3">(D11*100/I11)-100</f>
-        <v>-21.26882126882127</v>
+        <f t="shared" ref="J11:J15" si="3">(C11*100/I11)-100</f>
+        <v>-25.836325836325841</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -974,9 +994,11 @@
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>-7.4713797951395833</v>
-      </c>
-      <c r="C12" s="3"/>
+        <v>-38.919036249186021</v>
+      </c>
+      <c r="C12" s="11">
+        <v>2814</v>
+      </c>
       <c r="D12" s="11">
         <v>4607</v>
       </c>
@@ -997,7 +1019,7 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="3"/>
-        <v>-75.018978418826592</v>
+        <v>-84.741351263420455</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -1006,9 +1028,11 @@
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>0.93872891031332983</v>
-      </c>
-      <c r="C13" s="3"/>
+        <v>-30.451175065979641</v>
+      </c>
+      <c r="C13" s="11">
+        <v>5534</v>
+      </c>
       <c r="D13" s="11">
         <v>7957</v>
       </c>
@@ -1029,7 +1053,7 @@
       </c>
       <c r="J13" s="3">
         <f t="shared" si="3"/>
-        <v>-66.444566271665337</v>
+        <v>-76.662590140429302</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -1038,9 +1062,11 @@
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>31.83229813664596</v>
-      </c>
-      <c r="C14" s="3"/>
+        <v>-14.016489988221437</v>
+      </c>
+      <c r="C14" s="11">
+        <v>730</v>
+      </c>
       <c r="D14" s="11">
         <v>849</v>
       </c>
@@ -1061,7 +1087,7 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="3"/>
-        <v>-67.632481890964542</v>
+        <v>-72.169271826153263</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -1069,10 +1095,12 @@
         <v>5</v>
       </c>
       <c r="B15" s="3">
-        <f t="shared" si="2"/>
-        <v>28.365937859608749</v>
-      </c>
-      <c r="C15" s="3"/>
+        <f>(C15*100/D15)-100</f>
+        <v>-8.7180636485880711</v>
+      </c>
+      <c r="C15" s="11">
+        <v>4073</v>
+      </c>
       <c r="D15" s="11">
         <v>4462</v>
       </c>
@@ -1093,11 +1121,14 @@
       </c>
       <c r="J15" s="3">
         <f t="shared" si="3"/>
-        <v>-44.06418453052526</v>
-      </c>
+        <v>-48.940704525510846</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J16" s="14"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:C7">
+  <conditionalFormatting sqref="B2:B7">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
@@ -1111,7 +1142,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B10:C15">
+  <conditionalFormatting sqref="B10:B15">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
@@ -1182,7 +1213,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>B2:C7</xm:sqref>
+          <xm:sqref>B2:B7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{5DFD4702-AFA2-4D91-98CB-0AD8A93A7697}">
@@ -1195,7 +1226,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>B10:C15</xm:sqref>
+          <xm:sqref>B10:B15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{96C1573B-A030-48E0-B2A2-67E751F2AFDF}">
